--- a/data/WP17/WP17_sachgebiete_AfD.xlsx
+++ b/data/WP17/WP17_sachgebiete_AfD.xlsx
@@ -779,7 +779,7 @@
         <v>431</v>
       </c>
       <c r="D2" t="n">
-        <v>30.877030162413</v>
+        <v>30.8143851508121</v>
       </c>
       <c r="E2" t="n">
         <v>256</v>
@@ -1017,10 +1017,10 @@
         <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>30.2786885245902</v>
+        <v>30.5737704918033</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -3246,13 +3246,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C0B925-62D5-4B50-A3E8-E34AD8AFB59E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79353AF2-F8D0-4C18-B2D9-BF677543430E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D724A2E-A08A-48B1-ADEB-1ADAF9E4026C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20902A37-B4C2-4B9B-92DF-052C5FD061A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DECFCC91-7AA4-4254-BCE2-8F3C55BDFDFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A787569B-A11D-4D0F-9AA8-630E12492078}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_AfD.xlsx
+++ b/data/WP17/WP17_sachgebiete_AfD.xlsx
@@ -446,7 +446,7 @@
         <v>31.8491879350348</v>
       </c>
       <c r="E2" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>32.0925110132159</v>
       </c>
       <c r="E3" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>33.7030303030303</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>35.2074074074074</v>
       </c>
       <c r="E5" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>31.7207207207207</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         <v>37.9805825242718</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>36.1868131868132</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>28.2359550561798</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>25.7631578947368</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -616,7 +616,7 @@
         <v>29.6428571428571</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -650,7 +650,7 @@
         <v>30.2878787878788</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>32.8</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>31.983606557377</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>24.75</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -735,7 +735,7 @@
         <v>33.0243902439024</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -752,7 +752,7 @@
         <v>31.0975609756098</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>38.051282051282</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DB4C152-0C7E-4433-B685-90B7206BAE72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F72AC34-8AC8-4956-A8AA-6C1BC53D1E61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3237C09B-40BA-4F14-80AF-BE0B80726164}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A5231D-CA96-4571-BB6C-26369E1B5B24}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B6AA7D2-DDCA-4D56-875F-2F2047E30098}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4C05F3-9558-4056-A975-700A7B468D2A}"/>
 </file>